--- a/p3_data_preparation/data/argentina_south_america/df_etiquetas.xlsx
+++ b/p3_data_preparation/data/argentina_south_america/df_etiquetas.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D388"/>
+  <dimension ref="A1:D389"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3939,14 +3939,14 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>dt_vis</t>
+          <t>dt_loc</t>
         </is>
       </c>
       <c r="C220" t="n">
-        <v>0</v>
+        <v>164</v>
       </c>
       <c r="D220" t="n">
-        <v>0</v>
+        <v>164</v>
       </c>
     </row>
     <row r="221">
@@ -3959,10 +3959,10 @@
         </is>
       </c>
       <c r="C221" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D221" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="222">
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="C222" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D222" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="223">
@@ -3991,10 +3991,10 @@
         </is>
       </c>
       <c r="C223" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D223" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="224">
@@ -4007,10 +4007,10 @@
         </is>
       </c>
       <c r="C224" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D224" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="225">
@@ -4023,10 +4023,10 @@
         </is>
       </c>
       <c r="C225" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D225" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="226">
@@ -4039,10 +4039,10 @@
         </is>
       </c>
       <c r="C226" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D226" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="227">
@@ -4055,10 +4055,10 @@
         </is>
       </c>
       <c r="C227" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D227" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="228">
@@ -4071,10 +4071,10 @@
         </is>
       </c>
       <c r="C228" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D228" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="229">
@@ -4087,10 +4087,10 @@
         </is>
       </c>
       <c r="C229" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D229" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="230">
@@ -4103,10 +4103,10 @@
         </is>
       </c>
       <c r="C230" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D230" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="231">
@@ -4119,10 +4119,10 @@
         </is>
       </c>
       <c r="C231" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D231" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="232">
@@ -4135,10 +4135,10 @@
         </is>
       </c>
       <c r="C232" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D232" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="233">
@@ -4151,10 +4151,10 @@
         </is>
       </c>
       <c r="C233" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D233" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="234">
@@ -4167,10 +4167,10 @@
         </is>
       </c>
       <c r="C234" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D234" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="235">
@@ -4183,10 +4183,10 @@
         </is>
       </c>
       <c r="C235" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D235" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="236">
@@ -4199,10 +4199,10 @@
         </is>
       </c>
       <c r="C236" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D236" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="237">
@@ -4215,10 +4215,10 @@
         </is>
       </c>
       <c r="C237" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D237" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="238">
@@ -4231,10 +4231,10 @@
         </is>
       </c>
       <c r="C238" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D238" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="239">
@@ -4247,10 +4247,10 @@
         </is>
       </c>
       <c r="C239" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D239" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="240">
@@ -4263,10 +4263,10 @@
         </is>
       </c>
       <c r="C240" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D240" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="241">
@@ -4279,10 +4279,10 @@
         </is>
       </c>
       <c r="C241" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D241" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="242">
@@ -4295,10 +4295,10 @@
         </is>
       </c>
       <c r="C242" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D242" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="243">
@@ -4311,10 +4311,10 @@
         </is>
       </c>
       <c r="C243" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D243" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="244">
@@ -4327,10 +4327,10 @@
         </is>
       </c>
       <c r="C244" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D244" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="245">
@@ -4343,10 +4343,10 @@
         </is>
       </c>
       <c r="C245" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D245" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="246">
@@ -4359,10 +4359,10 @@
         </is>
       </c>
       <c r="C246" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D246" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="247">
@@ -4375,10 +4375,10 @@
         </is>
       </c>
       <c r="C247" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D247" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="248">
@@ -4391,10 +4391,10 @@
         </is>
       </c>
       <c r="C248" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D248" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="249">
@@ -4407,10 +4407,10 @@
         </is>
       </c>
       <c r="C249" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D249" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="250">
@@ -4423,10 +4423,10 @@
         </is>
       </c>
       <c r="C250" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D250" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="251">
@@ -4439,10 +4439,10 @@
         </is>
       </c>
       <c r="C251" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D251" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="252">
@@ -4455,10 +4455,10 @@
         </is>
       </c>
       <c r="C252" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D252" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="253">
@@ -4471,10 +4471,10 @@
         </is>
       </c>
       <c r="C253" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D253" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="254">
@@ -4487,10 +4487,10 @@
         </is>
       </c>
       <c r="C254" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D254" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="255">
@@ -4503,10 +4503,10 @@
         </is>
       </c>
       <c r="C255" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D255" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="256">
@@ -4519,10 +4519,10 @@
         </is>
       </c>
       <c r="C256" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D256" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="257">
@@ -4535,10 +4535,10 @@
         </is>
       </c>
       <c r="C257" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D257" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="258">
@@ -4551,10 +4551,10 @@
         </is>
       </c>
       <c r="C258" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D258" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="259">
@@ -4567,10 +4567,10 @@
         </is>
       </c>
       <c r="C259" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D259" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="260">
@@ -4583,10 +4583,10 @@
         </is>
       </c>
       <c r="C260" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D260" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="261">
@@ -4599,10 +4599,10 @@
         </is>
       </c>
       <c r="C261" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D261" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="262">
@@ -4615,10 +4615,10 @@
         </is>
       </c>
       <c r="C262" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D262" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="263">
@@ -4631,10 +4631,10 @@
         </is>
       </c>
       <c r="C263" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D263" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="264">
@@ -4647,10 +4647,10 @@
         </is>
       </c>
       <c r="C264" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D264" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="265">
@@ -4663,10 +4663,10 @@
         </is>
       </c>
       <c r="C265" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D265" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="266">
@@ -4679,10 +4679,10 @@
         </is>
       </c>
       <c r="C266" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D266" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="267">
@@ -4695,10 +4695,10 @@
         </is>
       </c>
       <c r="C267" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D267" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="268">
@@ -4711,10 +4711,10 @@
         </is>
       </c>
       <c r="C268" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D268" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="269">
@@ -4727,10 +4727,10 @@
         </is>
       </c>
       <c r="C269" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D269" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="270">
@@ -4743,10 +4743,10 @@
         </is>
       </c>
       <c r="C270" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D270" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="271">
@@ -4759,10 +4759,10 @@
         </is>
       </c>
       <c r="C271" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D271" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="272">
@@ -4775,10 +4775,10 @@
         </is>
       </c>
       <c r="C272" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D272" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="273">
@@ -4791,10 +4791,10 @@
         </is>
       </c>
       <c r="C273" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D273" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="274">
@@ -4807,10 +4807,10 @@
         </is>
       </c>
       <c r="C274" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D274" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="275">
@@ -4823,10 +4823,10 @@
         </is>
       </c>
       <c r="C275" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D275" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="276">
@@ -4839,10 +4839,10 @@
         </is>
       </c>
       <c r="C276" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D276" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="277">
@@ -4855,10 +4855,10 @@
         </is>
       </c>
       <c r="C277" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D277" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="278">
@@ -4871,10 +4871,10 @@
         </is>
       </c>
       <c r="C278" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D278" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="279">
@@ -4887,10 +4887,10 @@
         </is>
       </c>
       <c r="C279" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D279" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="280">
@@ -4903,10 +4903,10 @@
         </is>
       </c>
       <c r="C280" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D280" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="281">
@@ -4919,10 +4919,10 @@
         </is>
       </c>
       <c r="C281" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D281" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="282">
@@ -4935,10 +4935,10 @@
         </is>
       </c>
       <c r="C282" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D282" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="283">
@@ -4951,10 +4951,10 @@
         </is>
       </c>
       <c r="C283" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D283" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="284">
@@ -4967,10 +4967,10 @@
         </is>
       </c>
       <c r="C284" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D284" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="285">
@@ -4983,10 +4983,10 @@
         </is>
       </c>
       <c r="C285" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D285" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="286">
@@ -4999,10 +4999,10 @@
         </is>
       </c>
       <c r="C286" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D286" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="287">
@@ -5015,10 +5015,10 @@
         </is>
       </c>
       <c r="C287" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D287" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="288">
@@ -5031,10 +5031,10 @@
         </is>
       </c>
       <c r="C288" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D288" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="289">
@@ -5047,10 +5047,10 @@
         </is>
       </c>
       <c r="C289" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D289" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="290">
@@ -5063,10 +5063,10 @@
         </is>
       </c>
       <c r="C290" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D290" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="291">
@@ -5079,10 +5079,10 @@
         </is>
       </c>
       <c r="C291" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D291" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="292">
@@ -5095,10 +5095,10 @@
         </is>
       </c>
       <c r="C292" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D292" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="293">
@@ -5111,10 +5111,10 @@
         </is>
       </c>
       <c r="C293" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D293" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="294">
@@ -5127,10 +5127,10 @@
         </is>
       </c>
       <c r="C294" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D294" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="295">
@@ -5143,10 +5143,10 @@
         </is>
       </c>
       <c r="C295" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D295" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="296">
@@ -5159,10 +5159,10 @@
         </is>
       </c>
       <c r="C296" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D296" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="297">
@@ -5175,10 +5175,10 @@
         </is>
       </c>
       <c r="C297" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D297" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="298">
@@ -5191,10 +5191,10 @@
         </is>
       </c>
       <c r="C298" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D298" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="299">
@@ -5207,10 +5207,10 @@
         </is>
       </c>
       <c r="C299" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D299" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="300">
@@ -5223,10 +5223,10 @@
         </is>
       </c>
       <c r="C300" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D300" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="301">
@@ -5239,10 +5239,10 @@
         </is>
       </c>
       <c r="C301" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D301" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="302">
@@ -5255,10 +5255,10 @@
         </is>
       </c>
       <c r="C302" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D302" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="303">
@@ -5271,10 +5271,10 @@
         </is>
       </c>
       <c r="C303" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D303" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="304">
@@ -5287,10 +5287,10 @@
         </is>
       </c>
       <c r="C304" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D304" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="305">
@@ -5303,10 +5303,10 @@
         </is>
       </c>
       <c r="C305" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D305" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="306">
@@ -5319,10 +5319,10 @@
         </is>
       </c>
       <c r="C306" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D306" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="307">
@@ -5335,10 +5335,10 @@
         </is>
       </c>
       <c r="C307" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D307" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="308">
@@ -5351,10 +5351,10 @@
         </is>
       </c>
       <c r="C308" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D308" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="309">
@@ -5367,10 +5367,10 @@
         </is>
       </c>
       <c r="C309" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D309" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="310">
@@ -5383,10 +5383,10 @@
         </is>
       </c>
       <c r="C310" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D310" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="311">
@@ -5399,10 +5399,10 @@
         </is>
       </c>
       <c r="C311" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D311" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="312">
@@ -5415,10 +5415,10 @@
         </is>
       </c>
       <c r="C312" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D312" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="313">
@@ -5431,10 +5431,10 @@
         </is>
       </c>
       <c r="C313" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D313" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="314">
@@ -5447,10 +5447,10 @@
         </is>
       </c>
       <c r="C314" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D314" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="315">
@@ -5463,10 +5463,10 @@
         </is>
       </c>
       <c r="C315" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D315" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="316">
@@ -5479,10 +5479,10 @@
         </is>
       </c>
       <c r="C316" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D316" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="317">
@@ -5495,10 +5495,10 @@
         </is>
       </c>
       <c r="C317" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D317" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="318">
@@ -5511,10 +5511,10 @@
         </is>
       </c>
       <c r="C318" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D318" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="319">
@@ -5527,10 +5527,10 @@
         </is>
       </c>
       <c r="C319" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D319" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="320">
@@ -5543,10 +5543,10 @@
         </is>
       </c>
       <c r="C320" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D320" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="321">
@@ -5559,10 +5559,10 @@
         </is>
       </c>
       <c r="C321" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D321" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="322">
@@ -5575,10 +5575,10 @@
         </is>
       </c>
       <c r="C322" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D322" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="323">
@@ -5591,10 +5591,10 @@
         </is>
       </c>
       <c r="C323" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D323" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="324">
@@ -5607,10 +5607,10 @@
         </is>
       </c>
       <c r="C324" t="n">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D324" t="n">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="325">
@@ -5623,10 +5623,10 @@
         </is>
       </c>
       <c r="C325" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D325" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="326">
@@ -5639,10 +5639,10 @@
         </is>
       </c>
       <c r="C326" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D326" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="327">
@@ -5655,10 +5655,10 @@
         </is>
       </c>
       <c r="C327" t="n">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D327" t="n">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="328">
@@ -5671,10 +5671,10 @@
         </is>
       </c>
       <c r="C328" t="n">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D328" t="n">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="329">
@@ -5687,10 +5687,10 @@
         </is>
       </c>
       <c r="C329" t="n">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D329" t="n">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="330">
@@ -5703,10 +5703,10 @@
         </is>
       </c>
       <c r="C330" t="n">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D330" t="n">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="331">
@@ -5719,10 +5719,10 @@
         </is>
       </c>
       <c r="C331" t="n">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D331" t="n">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="332">
@@ -5735,10 +5735,10 @@
         </is>
       </c>
       <c r="C332" t="n">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D332" t="n">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="333">
@@ -5751,10 +5751,10 @@
         </is>
       </c>
       <c r="C333" t="n">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D333" t="n">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="334">
@@ -5767,10 +5767,10 @@
         </is>
       </c>
       <c r="C334" t="n">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D334" t="n">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="335">
@@ -5783,10 +5783,10 @@
         </is>
       </c>
       <c r="C335" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D335" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="336">
@@ -5799,10 +5799,10 @@
         </is>
       </c>
       <c r="C336" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D336" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="337">
@@ -5815,10 +5815,10 @@
         </is>
       </c>
       <c r="C337" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D337" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="338">
@@ -5831,10 +5831,10 @@
         </is>
       </c>
       <c r="C338" t="n">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D338" t="n">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="339">
@@ -5847,10 +5847,10 @@
         </is>
       </c>
       <c r="C339" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D339" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="340">
@@ -5863,10 +5863,10 @@
         </is>
       </c>
       <c r="C340" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D340" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="341">
@@ -5879,10 +5879,10 @@
         </is>
       </c>
       <c r="C341" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D341" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="342">
@@ -5895,10 +5895,10 @@
         </is>
       </c>
       <c r="C342" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D342" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="343">
@@ -5911,10 +5911,10 @@
         </is>
       </c>
       <c r="C343" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D343" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="344">
@@ -5927,10 +5927,10 @@
         </is>
       </c>
       <c r="C344" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D344" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="345">
@@ -5943,10 +5943,10 @@
         </is>
       </c>
       <c r="C345" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D345" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="346">
@@ -5959,10 +5959,10 @@
         </is>
       </c>
       <c r="C346" t="n">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D346" t="n">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="347">
@@ -5975,10 +5975,10 @@
         </is>
       </c>
       <c r="C347" t="n">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D347" t="n">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="348">
@@ -5991,10 +5991,10 @@
         </is>
       </c>
       <c r="C348" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D348" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="349">
@@ -6007,10 +6007,10 @@
         </is>
       </c>
       <c r="C349" t="n">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D349" t="n">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="350">
@@ -6023,10 +6023,10 @@
         </is>
       </c>
       <c r="C350" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D350" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="351">
@@ -6039,10 +6039,10 @@
         </is>
       </c>
       <c r="C351" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D351" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="352">
@@ -6055,10 +6055,10 @@
         </is>
       </c>
       <c r="C352" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D352" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="353">
@@ -6071,10 +6071,10 @@
         </is>
       </c>
       <c r="C353" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D353" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="354">
@@ -6087,10 +6087,10 @@
         </is>
       </c>
       <c r="C354" t="n">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D354" t="n">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="355">
@@ -6103,10 +6103,10 @@
         </is>
       </c>
       <c r="C355" t="n">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D355" t="n">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="356">
@@ -6119,10 +6119,10 @@
         </is>
       </c>
       <c r="C356" t="n">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D356" t="n">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="357">
@@ -6135,10 +6135,10 @@
         </is>
       </c>
       <c r="C357" t="n">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D357" t="n">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="358">
@@ -6151,10 +6151,10 @@
         </is>
       </c>
       <c r="C358" t="n">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D358" t="n">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="359">
@@ -6167,10 +6167,10 @@
         </is>
       </c>
       <c r="C359" t="n">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D359" t="n">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="360">
@@ -6183,10 +6183,10 @@
         </is>
       </c>
       <c r="C360" t="n">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D360" t="n">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="361">
@@ -6199,10 +6199,10 @@
         </is>
       </c>
       <c r="C361" t="n">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D361" t="n">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="362">
@@ -6215,10 +6215,10 @@
         </is>
       </c>
       <c r="C362" t="n">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D362" t="n">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="363">
@@ -6231,10 +6231,10 @@
         </is>
       </c>
       <c r="C363" t="n">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D363" t="n">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="364">
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="C364" t="n">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D364" t="n">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="365">
@@ -6263,10 +6263,10 @@
         </is>
       </c>
       <c r="C365" t="n">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D365" t="n">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="366">
@@ -6279,10 +6279,10 @@
         </is>
       </c>
       <c r="C366" t="n">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D366" t="n">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="367">
@@ -6295,10 +6295,10 @@
         </is>
       </c>
       <c r="C367" t="n">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D367" t="n">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="368">
@@ -6311,10 +6311,10 @@
         </is>
       </c>
       <c r="C368" t="n">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D368" t="n">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="369">
@@ -6327,10 +6327,10 @@
         </is>
       </c>
       <c r="C369" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D369" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="370">
@@ -6343,10 +6343,10 @@
         </is>
       </c>
       <c r="C370" t="n">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D370" t="n">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="371">
@@ -6359,10 +6359,10 @@
         </is>
       </c>
       <c r="C371" t="n">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D371" t="n">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="372">
@@ -6375,10 +6375,10 @@
         </is>
       </c>
       <c r="C372" t="n">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D372" t="n">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="373">
@@ -6391,10 +6391,10 @@
         </is>
       </c>
       <c r="C373" t="n">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D373" t="n">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="374">
@@ -6407,10 +6407,10 @@
         </is>
       </c>
       <c r="C374" t="n">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D374" t="n">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="375">
@@ -6423,10 +6423,10 @@
         </is>
       </c>
       <c r="C375" t="n">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D375" t="n">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="376">
@@ -6439,10 +6439,10 @@
         </is>
       </c>
       <c r="C376" t="n">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D376" t="n">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="377">
@@ -6455,10 +6455,10 @@
         </is>
       </c>
       <c r="C377" t="n">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D377" t="n">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="378">
@@ -6471,10 +6471,10 @@
         </is>
       </c>
       <c r="C378" t="n">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D378" t="n">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="379">
@@ -6487,10 +6487,10 @@
         </is>
       </c>
       <c r="C379" t="n">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D379" t="n">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="380">
@@ -6503,10 +6503,10 @@
         </is>
       </c>
       <c r="C380" t="n">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D380" t="n">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="381">
@@ -6519,10 +6519,10 @@
         </is>
       </c>
       <c r="C381" t="n">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D381" t="n">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="382">
@@ -6535,10 +6535,10 @@
         </is>
       </c>
       <c r="C382" t="n">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D382" t="n">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="383">
@@ -6551,10 +6551,10 @@
         </is>
       </c>
       <c r="C383" t="n">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D383" t="n">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="384">
@@ -6567,10 +6567,10 @@
         </is>
       </c>
       <c r="C384" t="n">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D384" t="n">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="385">
@@ -6583,10 +6583,10 @@
         </is>
       </c>
       <c r="C385" t="n">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D385" t="n">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="386">
@@ -6599,10 +6599,10 @@
         </is>
       </c>
       <c r="C386" t="n">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D386" t="n">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="387">
@@ -6615,10 +6615,10 @@
         </is>
       </c>
       <c r="C387" t="n">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D387" t="n">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="388">
@@ -6631,9 +6631,25 @@
         </is>
       </c>
       <c r="C388" t="n">
+        <v>167</v>
+      </c>
+      <c r="D388" t="n">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" s="1" t="n">
+        <v>387</v>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>dt_vis</t>
+        </is>
+      </c>
+      <c r="C389" t="n">
         <v>168</v>
       </c>
-      <c r="D388" t="n">
+      <c r="D389" t="n">
         <v>168</v>
       </c>
     </row>
